--- a/Progress Report.xlsx
+++ b/Progress Report.xlsx
@@ -3,7 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="49" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="416" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="49" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="65">
   <si>
     <t>Task</t>
   </si>
@@ -26,6 +27,128 @@
   </si>
   <si>
     <t>Date</t>
+  </si>
+  <si>
+    <t>PDM to PCM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Converts each 1-bit 3.072 MHz PDM signal from the microphones to a 16-bit 48kHz or 192kHz PCM audio 
+signal </t>
+  </si>
+  <si>
+    <t>Nate</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Last week</t>
+  </si>
+  <si>
+    <t>Time Difference of Arrival</t>
+  </si>
+  <si>
+    <t>Proof of concept block that determines potential locations in a 2-by-2 quadrant of possible locations</t>
+  </si>
+  <si>
+    <t>Sandeep</t>
+  </si>
+  <si>
+    <t>This week</t>
+  </si>
+  <si>
+    <t>LVMC Beamforming</t>
+  </si>
+  <si>
+    <t>Creating a covariance matrix and converting the values into possible displayable locations</t>
+  </si>
+  <si>
+    <t>Kailan, Sandeep, David, Srivibhav, Nate</t>
+  </si>
+  <si>
+    <t>Cross Covariance Calculation</t>
+  </si>
+  <si>
+    <t>Calculate the cross covariance matrix of the microphone data</t>
+  </si>
+  <si>
+    <t>Kailan</t>
+  </si>
+  <si>
+    <t>LCMV Weight Calculation</t>
+  </si>
+  <si>
+    <t>Module to calculate the LCMV output from the CC matrix and saved LCMV weights</t>
+  </si>
+  <si>
+    <t>In Progress</t>
+  </si>
+  <si>
+    <t>PL to PS Communication</t>
+  </si>
+  <si>
+    <t>Sending data from PL to PS to eventually use for locations -&gt; heatmap display path (HLS lightweight bridge)</t>
+  </si>
+  <si>
+    <t>David, Sandeep</t>
+  </si>
+  <si>
+    <t>Bandpass Filtering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select between several pre-determined FIR bandpass filters for analyzing a specific frequency window. 
+FIR filters also compsensate for CIC filter passband droop and intrinsic frequency response of microphones </t>
+  </si>
+  <si>
+    <t>Nate, Sri</t>
+  </si>
+  <si>
+    <t>Testing output of Microphones</t>
+  </si>
+  <si>
+    <t>Checking the output of the microphones gives reasonable recording from inducing a frequency tone</t>
+  </si>
+  <si>
+    <t>David, Nate, Srivibhav</t>
+  </si>
+  <si>
+    <t>Integration 2</t>
+  </si>
+  <si>
+    <t>Processed PCM mic audio data from PL to PS, output to Linux</t>
+  </si>
+  <si>
+    <t>Nate, Sri, David</t>
+  </si>
+  <si>
+    <t>Integration 3</t>
+  </si>
+  <si>
+    <t>TDOA proof of concept</t>
+  </si>
+  <si>
+    <t>Integration 4</t>
+  </si>
+  <si>
+    <t>Initial implementation of LVMC beamforming</t>
+  </si>
+  <si>
+    <t>Not Started</t>
+  </si>
+  <si>
+    <t>Next week</t>
+  </si>
+  <si>
+    <t>Sound Localization</t>
+  </si>
+  <si>
+    <t>Save the LCMV weights for each position on 3x3 grid</t>
+  </si>
+  <si>
+    <t>Heatmap Calculation</t>
+  </si>
+  <si>
+    <t>Calculate heatmap from based on what is received from PL side</t>
   </si>
   <si>
     <t>Microphone PCB</t>
@@ -33,12 +156,6 @@
   <si>
     <t>Design and assembly of 3 separate PCB boards in Altium. Boards use 3 styles of microphone arrays and allow 
 for interfacing mic data with FPGA</t>
-  </si>
-  <si>
-    <t>Nate</t>
-  </si>
-  <si>
-    <t>Done</t>
   </si>
   <si>
     <t>Previous weeks</t>
@@ -55,16 +172,6 @@
     <t>Srivibhav, Kailan</t>
   </si>
   <si>
-    <t>PDM to PCM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Converts each 1-bit 3.072 MHz PDM signal from the microphones to a 16-bit 48kHz or 192kHz PCM audio 
-signal </t>
-  </si>
-  <si>
-    <t>This week</t>
-  </si>
-  <si>
     <t>Linux Installation onto FPGA</t>
   </si>
   <si>
@@ -86,58 +193,9 @@
     <t>Setup computer vision to allow displaying over a USB camera</t>
   </si>
   <si>
-    <t>Kailan</t>
-  </si>
-  <si>
-    <t>Time Difference of Arrival</t>
-  </si>
-  <si>
-    <t>Proof of concept block that determines potential locations in a 2-by-2 quadrant of possible locations</t>
-  </si>
-  <si>
-    <t>Sandeep</t>
-  </si>
-  <si>
-    <t>In Progress</t>
-  </si>
-  <si>
-    <t>LVMC Beamforming</t>
-  </si>
-  <si>
-    <t>Creating a covariance matrix and converting the values into possible displayable locations</t>
-  </si>
-  <si>
-    <t>Kailan, Sandeep, David, Srivibhav, Nate</t>
-  </si>
-  <si>
-    <t>Cross Covariance Calculation</t>
-  </si>
-  <si>
-    <t>Calculate the cross covariance matrix of the microphone data</t>
-  </si>
-  <si>
     <t>LCMV Calculation</t>
   </si>
   <si>
-    <t>Module to calculate the LCMV output from the CC matrix and saved LCMV weights</t>
-  </si>
-  <si>
-    <t>PL to PS Communication</t>
-  </si>
-  <si>
-    <t>Sending data from PL to PS to eventually use for locations -&gt; heatmap display path (HLS lightweight bridge)</t>
-  </si>
-  <si>
-    <t>David, Sandeep</t>
-  </si>
-  <si>
-    <t>Bandpass Filtering</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select between several pre-determined FIR bandpass filters for analyzing a specific frequency window. 
-FIR filters also compsensate for CIC filter passband droop and intrinsic frequency response of microphones </t>
-  </si>
-  <si>
     <t>Creating Spreadsheet</t>
   </si>
   <si>
@@ -147,52 +205,10 @@
     <t>Kailan, Sandeep, Nate, Srivibhav</t>
   </si>
   <si>
-    <t>Testing output of Microphones</t>
-  </si>
-  <si>
-    <t>Checking the output of the microphones gives reasonable recording from inducing a frequency tone</t>
-  </si>
-  <si>
-    <t>David, Nate, Srivibhav</t>
-  </si>
-  <si>
     <t>Integration 1</t>
   </si>
   <si>
     <t>Basic Mic Output (PDM from PCB - Oscilliscope)</t>
-  </si>
-  <si>
-    <t>Nate, Sri, David</t>
-  </si>
-  <si>
-    <t>Integration 2</t>
-  </si>
-  <si>
-    <t>Processed PCM mic audio data from PL to PS, output to Linux</t>
-  </si>
-  <si>
-    <t>Integration 3</t>
-  </si>
-  <si>
-    <t>TDOA proof of concept</t>
-  </si>
-  <si>
-    <t>Not Started</t>
-  </si>
-  <si>
-    <t>Integration 4</t>
-  </si>
-  <si>
-    <t>Initial implementation of LVMC beamforming</t>
-  </si>
-  <si>
-    <t>Sound Localization</t>
-  </si>
-  <si>
-    <t>Save the LCMV weights for each position on 3x3 grid</t>
-  </si>
-  <si>
-    <t>Heatmap Calculation</t>
   </si>
   <si>
     <t>Calculate heatmap from LCMV matrix calculated on PL</t>
@@ -281,10 +297,10 @@
     <xf borderId="0" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="6" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -294,6 +310,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -502,6 +522,282 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
+    <col customWidth="1" min="1" max="1" width="28.25"/>
+    <col customWidth="1" min="2" max="2" width="84.38"/>
+    <col customWidth="1" min="3" max="3" width="31.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="6"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="6"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="6"/>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
     <col customWidth="1" min="1" max="1" width="29.38"/>
     <col customWidth="1" min="2" max="2" width="82.13"/>
     <col customWidth="1" min="3" max="3" width="34.88"/>
@@ -526,10 +822,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>7</v>
@@ -538,32 +834,32 @@
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" ht="32.25" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>12</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>7</v>
@@ -572,308 +868,308 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="5"/>
+        <v>12</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="6"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E19" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="6"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E20" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="6"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="5"/>
+        <v>19</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="6"/>
     </row>
     <row r="22">
-      <c r="A22" s="5"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="5"/>
+      <c r="E22" s="6"/>
     </row>
     <row r="23">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
+      <c r="A23" s="6"/>
+      <c r="B23" s="6"/>
+      <c r="C23" s="6"/>
       <c r="D23" s="2"/>
-      <c r="E23" s="5"/>
+      <c r="E23" s="6"/>
     </row>
     <row r="24">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="5"/>
+      <c r="E24" s="6"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
